--- a/D_analysis/check_output/IC_score.xlsx
+++ b/D_analysis/check_output/IC_score.xlsx
@@ -986,7 +986,7 @@
         <v>1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>0.5</v>
@@ -995,7 +995,7 @@
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2283,10 +2283,10 @@
         <v>82</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>0.5</v>

--- a/D_analysis/check_output/IC_score.xlsx
+++ b/D_analysis/check_output/IC_score.xlsx
@@ -2563,7 +2563,7 @@
         <v>96</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>0.5</v>
       </c>
       <c r="F92">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6">

--- a/D_analysis/check_output/IC_score.xlsx
+++ b/D_analysis/check_output/IC_score.xlsx
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>0.5</v>
@@ -2575,7 +2575,7 @@
         <v>0.5</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:6">

--- a/D_analysis/check_output/IC_score.xlsx
+++ b/D_analysis/check_output/IC_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>factor_id</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>V018</t>
+  </si>
+  <si>
+    <t>V023</t>
+  </si>
+  <si>
+    <t>V024</t>
   </si>
   <si>
     <t>W001</t>
@@ -735,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2563,10 +2569,10 @@
         <v>96</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0.5</v>
@@ -2766,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0.5</v>
@@ -2775,7 +2781,7 @@
         <v>0.5</v>
       </c>
       <c r="F102">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -2786,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0.5</v>
@@ -2795,7 +2801,7 @@
         <v>0.5</v>
       </c>
       <c r="F103">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -2826,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105">
         <v>0.5</v>
@@ -2835,7 +2841,7 @@
         <v>0.5</v>
       </c>
       <c r="F105">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -2886,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0.5</v>
@@ -2895,7 +2901,7 @@
         <v>0.5</v>
       </c>
       <c r="F108">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -2906,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0.5</v>
@@ -2915,7 +2921,7 @@
         <v>0.5</v>
       </c>
       <c r="F109">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -2926,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0.5</v>
@@ -2935,7 +2941,7 @@
         <v>0.5</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -2943,7 +2949,7 @@
         <v>115</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111">
         <v>1</v>
@@ -2955,7 +2961,7 @@
         <v>0.5</v>
       </c>
       <c r="F111">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -2966,7 +2972,7 @@
         <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>0.5</v>
@@ -2975,7 +2981,7 @@
         <v>0.5</v>
       </c>
       <c r="F112">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -2986,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>0.5</v>
@@ -2995,7 +3001,7 @@
         <v>0.5</v>
       </c>
       <c r="F113">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3003,7 +3009,7 @@
         <v>118</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -3015,7 +3021,7 @@
         <v>0.5</v>
       </c>
       <c r="F114">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3026,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0.5</v>
@@ -3035,7 +3041,7 @@
         <v>0.5</v>
       </c>
       <c r="F115">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3043,10 +3049,10 @@
         <v>120</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116">
         <v>0.5</v>
@@ -3055,7 +3061,7 @@
         <v>0.5</v>
       </c>
       <c r="F116">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3063,7 +3069,7 @@
         <v>121</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -3075,7 +3081,7 @@
         <v>0.5</v>
       </c>
       <c r="F117">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3103,19 +3109,19 @@
         <v>123</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3123,10 +3129,10 @@
         <v>124</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120">
         <v>0.5</v>
@@ -3135,7 +3141,7 @@
         <v>0.5</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3143,19 +3149,19 @@
         <v>125</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F121">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3186,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>0.5</v>
@@ -3195,7 +3201,7 @@
         <v>0.5</v>
       </c>
       <c r="F123">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3203,7 +3209,7 @@
         <v>128</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -3215,7 +3221,7 @@
         <v>0.5</v>
       </c>
       <c r="F124">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3226,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>0.5</v>
@@ -3235,6 +3241,46 @@
         <v>0.5</v>
       </c>
       <c r="F125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>130</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0.5</v>
+      </c>
+      <c r="E126">
+        <v>0.5</v>
+      </c>
+      <c r="F126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>131</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>0.5</v>
+      </c>
+      <c r="E127">
+        <v>0.5</v>
+      </c>
+      <c r="F127">
         <v>3</v>
       </c>
     </row>

--- a/D_analysis/check_output/IC_score.xlsx
+++ b/D_analysis/check_output/IC_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="232">
   <si>
     <t>factor_id</t>
   </si>
@@ -34,6 +34,54 @@
     <t>总分</t>
   </si>
   <si>
+    <t>C001</t>
+  </si>
+  <si>
+    <t>C002</t>
+  </si>
+  <si>
+    <t>C003</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>C005</t>
+  </si>
+  <si>
+    <t>C009</t>
+  </si>
+  <si>
+    <t>C012</t>
+  </si>
+  <si>
+    <t>C015</t>
+  </si>
+  <si>
+    <t>C017</t>
+  </si>
+  <si>
+    <t>C018</t>
+  </si>
+  <si>
+    <t>C019</t>
+  </si>
+  <si>
+    <t>C024</t>
+  </si>
+  <si>
+    <t>C026</t>
+  </si>
+  <si>
+    <t>C030</t>
+  </si>
+  <si>
+    <t>C031</t>
+  </si>
+  <si>
+    <t>C032</t>
+  </si>
+  <si>
     <t>D001</t>
   </si>
   <si>
@@ -49,6 +97,54 @@
     <t>D008</t>
   </si>
   <si>
+    <t>D009</t>
+  </si>
+  <si>
+    <t>D010</t>
+  </si>
+  <si>
+    <t>D011</t>
+  </si>
+  <si>
+    <t>D012</t>
+  </si>
+  <si>
+    <t>D013</t>
+  </si>
+  <si>
+    <t>D014</t>
+  </si>
+  <si>
+    <t>D015</t>
+  </si>
+  <si>
+    <t>D016</t>
+  </si>
+  <si>
+    <t>D017</t>
+  </si>
+  <si>
+    <t>D018</t>
+  </si>
+  <si>
+    <t>D019</t>
+  </si>
+  <si>
+    <t>D020</t>
+  </si>
+  <si>
+    <t>D021</t>
+  </si>
+  <si>
+    <t>D022</t>
+  </si>
+  <si>
+    <t>D023</t>
+  </si>
+  <si>
+    <t>D025</t>
+  </si>
+  <si>
     <t>F001</t>
   </si>
   <si>
@@ -67,6 +163,69 @@
     <t>F006</t>
   </si>
   <si>
+    <t>F007</t>
+  </si>
+  <si>
+    <t>F008</t>
+  </si>
+  <si>
+    <t>F009</t>
+  </si>
+  <si>
+    <t>F010</t>
+  </si>
+  <si>
+    <t>F011</t>
+  </si>
+  <si>
+    <t>F012</t>
+  </si>
+  <si>
+    <t>F013</t>
+  </si>
+  <si>
+    <t>F014</t>
+  </si>
+  <si>
+    <t>F015</t>
+  </si>
+  <si>
+    <t>F016</t>
+  </si>
+  <si>
+    <t>F017</t>
+  </si>
+  <si>
+    <t>F018</t>
+  </si>
+  <si>
+    <t>F019</t>
+  </si>
+  <si>
+    <t>F020</t>
+  </si>
+  <si>
+    <t>F021</t>
+  </si>
+  <si>
+    <t>F022</t>
+  </si>
+  <si>
+    <t>F023</t>
+  </si>
+  <si>
+    <t>F024</t>
+  </si>
+  <si>
+    <t>F025</t>
+  </si>
+  <si>
+    <t>F026</t>
+  </si>
+  <si>
+    <t>F029</t>
+  </si>
+  <si>
     <t>G001</t>
   </si>
   <si>
@@ -127,6 +286,135 @@
     <t>G024</t>
   </si>
   <si>
+    <t>G025</t>
+  </si>
+  <si>
+    <t>G026</t>
+  </si>
+  <si>
+    <t>G027</t>
+  </si>
+  <si>
+    <t>G028</t>
+  </si>
+  <si>
+    <t>G029</t>
+  </si>
+  <si>
+    <t>G030</t>
+  </si>
+  <si>
+    <t>G031</t>
+  </si>
+  <si>
+    <t>G032</t>
+  </si>
+  <si>
+    <t>G033</t>
+  </si>
+  <si>
+    <t>G034</t>
+  </si>
+  <si>
+    <t>G035</t>
+  </si>
+  <si>
+    <t>G036</t>
+  </si>
+  <si>
+    <t>G037</t>
+  </si>
+  <si>
+    <t>G038</t>
+  </si>
+  <si>
+    <t>G039</t>
+  </si>
+  <si>
+    <t>G042</t>
+  </si>
+  <si>
+    <t>G043</t>
+  </si>
+  <si>
+    <t>G044</t>
+  </si>
+  <si>
+    <t>G045</t>
+  </si>
+  <si>
+    <t>G046</t>
+  </si>
+  <si>
+    <t>G048</t>
+  </si>
+  <si>
+    <t>G049</t>
+  </si>
+  <si>
+    <t>G050</t>
+  </si>
+  <si>
+    <t>G051</t>
+  </si>
+  <si>
+    <t>G052</t>
+  </si>
+  <si>
+    <t>G053</t>
+  </si>
+  <si>
+    <t>G054</t>
+  </si>
+  <si>
+    <t>G055</t>
+  </si>
+  <si>
+    <t>G056</t>
+  </si>
+  <si>
+    <t>G057</t>
+  </si>
+  <si>
+    <t>G058</t>
+  </si>
+  <si>
+    <t>G059</t>
+  </si>
+  <si>
+    <t>G060</t>
+  </si>
+  <si>
+    <t>G061</t>
+  </si>
+  <si>
+    <t>G062</t>
+  </si>
+  <si>
+    <t>G063</t>
+  </si>
+  <si>
+    <t>G064</t>
+  </si>
+  <si>
+    <t>G065</t>
+  </si>
+  <si>
+    <t>G066</t>
+  </si>
+  <si>
+    <t>G067</t>
+  </si>
+  <si>
+    <t>G068</t>
+  </si>
+  <si>
+    <t>G069</t>
+  </si>
+  <si>
+    <t>G070</t>
+  </si>
+  <si>
     <t>I001</t>
   </si>
   <si>
@@ -334,12 +622,6 @@
     <t>V018</t>
   </si>
   <si>
-    <t>V023</t>
-  </si>
-  <si>
-    <t>V024</t>
-  </si>
-  <si>
     <t>W001</t>
   </si>
   <si>
@@ -352,16 +634,34 @@
     <t>W003_G</t>
   </si>
   <si>
+    <t>W003_G_signal</t>
+  </si>
+  <si>
     <t>W003_I</t>
   </si>
   <si>
+    <t>W003_I_signal</t>
+  </si>
+  <si>
     <t>W003_P</t>
   </si>
   <si>
+    <t>W003_P_signal</t>
+  </si>
+  <si>
     <t>W003_V</t>
   </si>
   <si>
+    <t>W003_V_signal</t>
+  </si>
+  <si>
     <t>W003_W</t>
+  </si>
+  <si>
+    <t>W003_W_signal</t>
+  </si>
+  <si>
+    <t>W003_signal</t>
   </si>
   <si>
     <t>W004</t>
@@ -741,7 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F228"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -772,16 +1072,16 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -792,16 +1092,16 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -829,7 +1129,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -838,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -849,19 +1149,19 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -872,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>0.5</v>
@@ -881,7 +1181,7 @@
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -892,16 +1192,16 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -915,13 +1215,13 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -938,10 +1238,10 @@
         <v>0.5</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -958,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -989,19 +1289,19 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1009,7 +1309,7 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1021,7 +1321,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1032,16 +1332,16 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1055,13 +1355,13 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1089,16 +1389,16 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
         <v>2</v>
@@ -1112,16 +1412,16 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1129,7 +1429,7 @@
         <v>24</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1141,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1155,13 +1455,13 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1175,13 +1475,13 @@
         <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1189,19 +1489,19 @@
         <v>27</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1209,19 +1509,19 @@
         <v>28</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1258,10 +1558,10 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1272,16 +1572,16 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E27">
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1289,19 +1589,19 @@
         <v>32</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1312,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0.5</v>
@@ -1321,7 +1621,7 @@
         <v>0.5</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1332,16 +1632,16 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1375,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1389,7 +1689,7 @@
         <v>37</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1401,7 +1701,7 @@
         <v>0.5</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1409,19 +1709,19 @@
         <v>38</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1438,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1452,16 +1752,16 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E36">
         <v>0.5</v>
       </c>
       <c r="F36">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1489,19 +1789,19 @@
         <v>42</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -1509,10 +1809,10 @@
         <v>43</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0.5</v>
@@ -1521,7 +1821,7 @@
         <v>0.5</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1538,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -1572,13 +1872,13 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -1589,19 +1889,19 @@
         <v>47</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -1612,13 +1912,13 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -1632,16 +1932,16 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E45">
         <v>0.5</v>
       </c>
       <c r="F45">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -1652,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>0.5</v>
@@ -1661,7 +1961,7 @@
         <v>0.5</v>
       </c>
       <c r="F46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -1675,13 +1975,13 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E47">
         <v>0.5</v>
       </c>
       <c r="F47">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -1698,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1712,16 +2012,16 @@
         <v>0</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1735,13 +2035,13 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1769,19 +2069,19 @@
         <v>56</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0.5</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F52">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1789,19 +2089,19 @@
         <v>57</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -1855,13 +2155,13 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -1892,16 +2192,16 @@
         <v>0</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E58">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -1918,10 +2218,10 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -1932,16 +2232,16 @@
         <v>0</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E60">
         <v>0.5</v>
       </c>
       <c r="F60">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -1949,19 +2249,19 @@
         <v>65</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E61">
         <v>0.5</v>
       </c>
       <c r="F61">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -1969,19 +2269,19 @@
         <v>66</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E62">
         <v>0.5</v>
       </c>
       <c r="F62">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -1992,16 +2292,16 @@
         <v>0</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2012,16 +2312,16 @@
         <v>0</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E64">
         <v>0.5</v>
       </c>
       <c r="F64">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2035,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E65">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2049,19 +2349,19 @@
         <v>70</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E66">
         <v>0.5</v>
       </c>
       <c r="F66">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2075,18 +2375,18 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -2098,55 +2398,55 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
         <v>0.5</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F70">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -2166,13 +2466,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2181,15 +2481,15 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2198,18 +2498,18 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2221,12 +2521,12 @@
         <v>0</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -2246,7 +2546,7 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -2255,78 +2555,78 @@
         <v>1</v>
       </c>
       <c r="D76">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -2346,87 +2646,87 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81">
         <v>0</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84">
         <v>0</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -2435,18 +2735,18 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -2455,24 +2755,24 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0.5</v>
       </c>
       <c r="F86">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -2481,58 +2781,58 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F89">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -2541,32 +2841,32 @@
         <v>0</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E91">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -2575,78 +2875,78 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E92">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F92">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93">
         <v>0</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E93">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -2658,15 +2958,15 @@
         <v>0.5</v>
       </c>
       <c r="E96">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -2675,18 +2975,18 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2695,18 +2995,18 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F98">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -2726,33 +3026,33 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100">
         <v>0</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0.5</v>
@@ -2766,13 +3066,13 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102">
         <v>0.5</v>
@@ -2786,13 +3086,13 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0.5</v>
@@ -2806,13 +3106,13 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0.5</v>
@@ -2821,15 +3121,15 @@
         <v>0.5</v>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -2841,38 +3141,38 @@
         <v>0.5</v>
       </c>
       <c r="F105">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106">
         <v>1</v>
       </c>
       <c r="D106">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>0.5</v>
       </c>
       <c r="F106">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>0.5</v>
@@ -2886,33 +3186,33 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E108">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F108">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109">
         <v>0.5</v>
@@ -2926,33 +3226,33 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E110">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0.5</v>
@@ -2961,32 +3261,32 @@
         <v>0.5</v>
       </c>
       <c r="F111">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112">
         <v>1</v>
       </c>
       <c r="D112">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E112">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F112">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -2998,21 +3298,21 @@
         <v>0.5</v>
       </c>
       <c r="E113">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F113">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0.5</v>
@@ -3021,18 +3321,18 @@
         <v>0.5</v>
       </c>
       <c r="F114">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>0.5</v>
@@ -3041,38 +3341,38 @@
         <v>0.5</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0.5</v>
@@ -3081,72 +3381,72 @@
         <v>0.5</v>
       </c>
       <c r="F117">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F118">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
       <c r="D120">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F120">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -3155,18 +3455,18 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3186,27 +3486,27 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E123">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F123">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -3218,35 +3518,35 @@
         <v>0.5</v>
       </c>
       <c r="E124">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E125">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -3255,32 +3555,2052 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F126">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0.5</v>
+      </c>
+      <c r="F127">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
         <v>131</v>
       </c>
-      <c r="B127">
-        <v>1</v>
-      </c>
-      <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="D127">
-        <v>0.5</v>
-      </c>
-      <c r="E127">
-        <v>0.5</v>
-      </c>
-      <c r="F127">
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128">
+        <v>0.5</v>
+      </c>
+      <c r="E128">
+        <v>0.5</v>
+      </c>
+      <c r="F128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130">
+        <v>0.5</v>
+      </c>
+      <c r="E130">
+        <v>0.5</v>
+      </c>
+      <c r="F130">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>0.5</v>
+      </c>
+      <c r="E131">
+        <v>0.5</v>
+      </c>
+      <c r="F131">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>0.5</v>
+      </c>
+      <c r="F132">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0.5</v>
+      </c>
+      <c r="F133">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0.5</v>
+      </c>
+      <c r="F134">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136">
+        <v>0.5</v>
+      </c>
+      <c r="E136">
+        <v>0.5</v>
+      </c>
+      <c r="F136">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>0.5</v>
+      </c>
+      <c r="F137">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>0.5</v>
+      </c>
+      <c r="F142">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0.5</v>
+      </c>
+      <c r="E143">
+        <v>0.5</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>0.5</v>
+      </c>
+      <c r="F144">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>0.5</v>
+      </c>
+      <c r="F145">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0.5</v>
+      </c>
+      <c r="E148">
+        <v>0.5</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>0.5</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150">
+        <v>0.5</v>
+      </c>
+      <c r="E150">
+        <v>0.5</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>0.5</v>
+      </c>
+      <c r="E151">
+        <v>0.5</v>
+      </c>
+      <c r="F151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>0.5</v>
+      </c>
+      <c r="E152">
+        <v>0.5</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0.5</v>
+      </c>
+      <c r="E153">
+        <v>0.5</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>0.5</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>0.5</v>
+      </c>
+      <c r="F155">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>0.5</v>
+      </c>
+      <c r="F156">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>0.5</v>
+      </c>
+      <c r="F157">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>0.5</v>
+      </c>
+      <c r="F158">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>0.5</v>
+      </c>
+      <c r="F159">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>0.5</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>0.5</v>
+      </c>
+      <c r="F161">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>0.5</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0.5</v>
+      </c>
+      <c r="F163">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>0.5</v>
+      </c>
+      <c r="E164">
+        <v>0.5</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0.5</v>
+      </c>
+      <c r="F165">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>170</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167">
+        <v>0.5</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>171</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168">
+        <v>0.5</v>
+      </c>
+      <c r="E168">
+        <v>0.5</v>
+      </c>
+      <c r="F168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>172</v>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>173</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>174</v>
+      </c>
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>175</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <v>0.5</v>
+      </c>
+      <c r="E172">
+        <v>0.5</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>176</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>0.5</v>
+      </c>
+      <c r="E173">
+        <v>0.5</v>
+      </c>
+      <c r="F173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>177</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="D174">
+        <v>0.5</v>
+      </c>
+      <c r="E174">
+        <v>0.5</v>
+      </c>
+      <c r="F174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175">
+        <v>0.5</v>
+      </c>
+      <c r="E175">
+        <v>0.5</v>
+      </c>
+      <c r="F175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>179</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176">
+        <v>0.5</v>
+      </c>
+      <c r="E176">
+        <v>0.5</v>
+      </c>
+      <c r="F176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+      <c r="D179">
+        <v>0.5</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>0.5</v>
+      </c>
+      <c r="E181">
+        <v>0.5</v>
+      </c>
+      <c r="F181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182">
+        <v>0.5</v>
+      </c>
+      <c r="E182">
+        <v>0.5</v>
+      </c>
+      <c r="F182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183">
+        <v>0.5</v>
+      </c>
+      <c r="E183">
+        <v>0.5</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185">
+        <v>1</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>189</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="F186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>190</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="F187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>191</v>
+      </c>
+      <c r="B188">
+        <v>1</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188">
+        <v>0.5</v>
+      </c>
+      <c r="E188">
+        <v>0.5</v>
+      </c>
+      <c r="F188">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189">
+        <v>1</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>0.5</v>
+      </c>
+      <c r="E189">
+        <v>0.5</v>
+      </c>
+      <c r="F189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>193</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190">
+        <v>0.5</v>
+      </c>
+      <c r="E190">
+        <v>0.5</v>
+      </c>
+      <c r="F190">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>0.5</v>
+      </c>
+      <c r="E191">
+        <v>0.5</v>
+      </c>
+      <c r="F191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
+      <c r="F192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>0.5</v>
+      </c>
+      <c r="E193">
+        <v>0.5</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+      <c r="C194">
+        <v>1</v>
+      </c>
+      <c r="D194">
+        <v>0.5</v>
+      </c>
+      <c r="E194">
+        <v>0.5</v>
+      </c>
+      <c r="F194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+      <c r="C195">
+        <v>1</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+      <c r="F195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+      <c r="C196">
+        <v>1</v>
+      </c>
+      <c r="D196">
+        <v>0.5</v>
+      </c>
+      <c r="E196">
+        <v>0.5</v>
+      </c>
+      <c r="F196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+      <c r="D197">
+        <v>0.5</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0.5</v>
+      </c>
+      <c r="E198">
+        <v>0.5</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+      <c r="C199">
+        <v>1</v>
+      </c>
+      <c r="D199">
+        <v>0.5</v>
+      </c>
+      <c r="E199">
+        <v>0.5</v>
+      </c>
+      <c r="F199">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200">
+        <v>1</v>
+      </c>
+      <c r="C200">
+        <v>1</v>
+      </c>
+      <c r="D200">
+        <v>0.5</v>
+      </c>
+      <c r="E200">
+        <v>0.5</v>
+      </c>
+      <c r="F200">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201">
+        <v>1</v>
+      </c>
+      <c r="C201">
+        <v>1</v>
+      </c>
+      <c r="D201">
+        <v>0.5</v>
+      </c>
+      <c r="E201">
+        <v>0.5</v>
+      </c>
+      <c r="F201">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>205</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>0.5</v>
+      </c>
+      <c r="E202">
+        <v>0.5</v>
+      </c>
+      <c r="F202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>206</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+      <c r="C203">
+        <v>1</v>
+      </c>
+      <c r="D203">
+        <v>0.5</v>
+      </c>
+      <c r="E203">
+        <v>0.5</v>
+      </c>
+      <c r="F203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204">
+        <v>1</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204">
+        <v>0.5</v>
+      </c>
+      <c r="E204">
+        <v>0.5</v>
+      </c>
+      <c r="F204">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>208</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205">
+        <v>0.5</v>
+      </c>
+      <c r="E205">
+        <v>0.5</v>
+      </c>
+      <c r="F205">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>209</v>
+      </c>
+      <c r="B206">
+        <v>1</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206">
+        <v>0.5</v>
+      </c>
+      <c r="E206">
+        <v>0.5</v>
+      </c>
+      <c r="F206">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>210</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>0.5</v>
+      </c>
+      <c r="E207">
+        <v>0.5</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>211</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>0.5</v>
+      </c>
+      <c r="E208">
+        <v>0.5</v>
+      </c>
+      <c r="F208">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>212</v>
+      </c>
+      <c r="B209">
+        <v>1</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>0.5</v>
+      </c>
+      <c r="E209">
+        <v>0.5</v>
+      </c>
+      <c r="F209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>213</v>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+      <c r="D210">
+        <v>0.5</v>
+      </c>
+      <c r="E210">
+        <v>0.5</v>
+      </c>
+      <c r="F210">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>214</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
+      </c>
+      <c r="D211">
+        <v>0.5</v>
+      </c>
+      <c r="E211">
+        <v>0.5</v>
+      </c>
+      <c r="F211">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>215</v>
+      </c>
+      <c r="B212">
+        <v>1</v>
+      </c>
+      <c r="C212">
+        <v>1</v>
+      </c>
+      <c r="D212">
+        <v>0.5</v>
+      </c>
+      <c r="E212">
+        <v>0.5</v>
+      </c>
+      <c r="F212">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>216</v>
+      </c>
+      <c r="B213">
+        <v>1</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213">
+        <v>0.5</v>
+      </c>
+      <c r="E213">
+        <v>0.5</v>
+      </c>
+      <c r="F213">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>217</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+      <c r="C214">
+        <v>1</v>
+      </c>
+      <c r="D214">
+        <v>0.5</v>
+      </c>
+      <c r="E214">
+        <v>0.5</v>
+      </c>
+      <c r="F214">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>218</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>0.5</v>
+      </c>
+      <c r="E215">
+        <v>0.5</v>
+      </c>
+      <c r="F215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>219</v>
+      </c>
+      <c r="B216">
+        <v>0</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>0.5</v>
+      </c>
+      <c r="E216">
+        <v>0.5</v>
+      </c>
+      <c r="F216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" t="s">
+        <v>220</v>
+      </c>
+      <c r="B217">
+        <v>0</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>0.5</v>
+      </c>
+      <c r="E217">
+        <v>0.5</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>1</v>
+      </c>
+      <c r="D218">
+        <v>0.5</v>
+      </c>
+      <c r="E218">
+        <v>0.5</v>
+      </c>
+      <c r="F218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" t="s">
+        <v>222</v>
+      </c>
+      <c r="B219">
+        <v>1</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+      <c r="D219">
+        <v>0.5</v>
+      </c>
+      <c r="E219">
+        <v>0.5</v>
+      </c>
+      <c r="F219">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220">
+        <v>1</v>
+      </c>
+      <c r="D220">
+        <v>0.5</v>
+      </c>
+      <c r="E220">
+        <v>0.5</v>
+      </c>
+      <c r="F220">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" t="s">
+        <v>224</v>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+      <c r="D221">
+        <v>0.5</v>
+      </c>
+      <c r="E221">
+        <v>0.5</v>
+      </c>
+      <c r="F221">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" t="s">
+        <v>225</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" t="s">
+        <v>226</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0.5</v>
+      </c>
+      <c r="E223">
+        <v>0.5</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" t="s">
+        <v>227</v>
+      </c>
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+      <c r="D224">
+        <v>0.5</v>
+      </c>
+      <c r="E224">
+        <v>0.5</v>
+      </c>
+      <c r="F224">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" t="s">
+        <v>228</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0.5</v>
+      </c>
+      <c r="E225">
+        <v>0.5</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>229</v>
+      </c>
+      <c r="B226">
+        <v>1</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>0.5</v>
+      </c>
+      <c r="E226">
+        <v>0.5</v>
+      </c>
+      <c r="F226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>230</v>
+      </c>
+      <c r="B227">
+        <v>1</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0.5</v>
+      </c>
+      <c r="E227">
+        <v>0.5</v>
+      </c>
+      <c r="F227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>231</v>
+      </c>
+      <c r="B228">
+        <v>1</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228">
+        <v>0.5</v>
+      </c>
+      <c r="E228">
+        <v>0.5</v>
+      </c>
+      <c r="F228">
         <v>3</v>
       </c>
     </row>

--- a/D_analysis/check_output/IC_score.xlsx
+++ b/D_analysis/check_output/IC_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="240">
   <si>
     <t>factor_id</t>
   </si>
@@ -457,6 +457,24 @@
     <t>I025</t>
   </si>
   <si>
+    <t>I057</t>
+  </si>
+  <si>
+    <t>I058</t>
+  </si>
+  <si>
+    <t>I059</t>
+  </si>
+  <si>
+    <t>I060</t>
+  </si>
+  <si>
+    <t>I061</t>
+  </si>
+  <si>
+    <t>I072</t>
+  </si>
+  <si>
     <t>L003</t>
   </si>
   <si>
@@ -710,6 +728,12 @@
   </si>
   <si>
     <t>W004_signal</t>
+  </si>
+  <si>
+    <t>W005_binary</t>
+  </si>
+  <si>
+    <t>W006_binary</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F228"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2352,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0.5</v>
@@ -2361,58 +2385,58 @@
         <v>0.5</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67">
         <v>0</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69">
         <v>0</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0.5</v>
@@ -2421,58 +2445,58 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0.5</v>
       </c>
       <c r="E70">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B71">
         <v>0</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -2481,12 +2505,12 @@
         <v>0</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2495,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E73">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>0.5</v>
@@ -2506,7 +2530,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2515,24 +2539,24 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
         <v>0.5</v>
@@ -2541,15 +2565,15 @@
         <v>0.5</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -2561,15 +2585,15 @@
         <v>0</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2578,18 +2602,18 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F77">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2601,12 +2625,12 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -2615,24 +2639,24 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -2641,38 +2665,38 @@
         <v>0</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F81">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -2681,32 +2705,32 @@
         <v>0</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F83">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -2726,47 +2750,47 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B85">
         <v>0</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -2775,58 +2799,58 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -2838,21 +2862,21 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -2866,53 +2890,53 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -2921,15 +2945,15 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2938,41 +2962,41 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F95">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>0</v>
       </c>
       <c r="F96">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -2981,12 +3005,12 @@
         <v>0</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -2995,38 +3019,38 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F98">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0.5</v>
       </c>
       <c r="F99">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3035,18 +3059,18 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3055,18 +3079,18 @@
         <v>1</v>
       </c>
       <c r="D101">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3086,7 +3110,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3106,27 +3130,27 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F104">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3146,7 +3170,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3155,18 +3179,18 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E106">
         <v>0.5</v>
       </c>
       <c r="F106">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3186,27 +3210,27 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3226,33 +3250,33 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B110">
         <v>0</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>0.5</v>
@@ -3261,18 +3285,18 @@
         <v>0.5</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
         <v>0</v>
@@ -3281,12 +3305,12 @@
         <v>0</v>
       </c>
       <c r="F112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3298,41 +3322,41 @@
         <v>0.5</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F113">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0.5</v>
@@ -3341,15 +3365,15 @@
         <v>0.5</v>
       </c>
       <c r="F115">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -3361,75 +3385,75 @@
         <v>0</v>
       </c>
       <c r="F116">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117">
         <v>0.5</v>
       </c>
       <c r="E117">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F119">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -3441,18 +3465,18 @@
         <v>0</v>
       </c>
       <c r="F120">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B121">
         <v>0</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>0.5</v>
@@ -3461,12 +3485,12 @@
         <v>0.5</v>
       </c>
       <c r="F121">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -3475,18 +3499,18 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -3506,27 +3530,27 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -3535,30 +3559,30 @@
         <v>1</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -3566,53 +3590,53 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F127">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>0.5</v>
       </c>
       <c r="E128">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F128">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -3621,32 +3645,32 @@
         <v>0</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -3655,98 +3679,98 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>0.5</v>
       </c>
       <c r="F131">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E132">
         <v>0.5</v>
       </c>
       <c r="F132">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B133">
         <v>0</v>
       </c>
       <c r="C133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F133">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E134">
         <v>0.5</v>
       </c>
       <c r="F134">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F135">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -3766,87 +3790,87 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E137">
         <v>0.5</v>
       </c>
       <c r="F137">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139">
         <v>1</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F139">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F140">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -3855,24 +3879,24 @@
         <v>1</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F141">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B142">
         <v>0</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -3881,12 +3905,12 @@
         <v>0.5</v>
       </c>
       <c r="F142">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -3895,21 +3919,21 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>0.5</v>
       </c>
       <c r="F143">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -3918,35 +3942,35 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F144">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E145">
         <v>0.5</v>
       </c>
       <c r="F145">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -3958,15 +3982,15 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -3986,19 +4010,19 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E148">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -4006,27 +4030,27 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D149">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -4035,44 +4059,44 @@
         <v>1</v>
       </c>
       <c r="D150">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E150">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B151">
         <v>0</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D151">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>0.5</v>
       </c>
       <c r="F151">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B152">
         <v>0</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>0.5</v>
@@ -4081,32 +4105,32 @@
         <v>0.5</v>
       </c>
       <c r="F152">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -4118,95 +4142,95 @@
         <v>0.5</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F154">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="B155">
         <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E155">
         <v>0.5</v>
       </c>
       <c r="F155">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E156">
         <v>0.5</v>
       </c>
       <c r="F156">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B157">
         <v>0</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E157">
         <v>0.5</v>
       </c>
       <c r="F157">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B158">
         <v>0</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F158">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -4226,7 +4250,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -4235,10 +4259,10 @@
         <v>0</v>
       </c>
       <c r="D160">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F160">
         <v>0.5</v>
@@ -4246,7 +4270,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -4258,15 +4282,15 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F161">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -4275,18 +4299,18 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E162">
         <v>0</v>
       </c>
       <c r="F162">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -4295,18 +4319,18 @@
         <v>0</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E163">
         <v>0.5</v>
       </c>
       <c r="F163">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -4318,55 +4342,55 @@
         <v>0.5</v>
       </c>
       <c r="E164">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B165">
         <v>0</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E165">
         <v>0.5</v>
       </c>
       <c r="F165">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E166">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F166">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -4378,21 +4402,21 @@
         <v>0.5</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F167">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B168">
         <v>0</v>
       </c>
       <c r="C168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168">
         <v>0.5</v>
@@ -4401,35 +4425,35 @@
         <v>0.5</v>
       </c>
       <c r="F168">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E169">
         <v>0</v>
       </c>
       <c r="F169">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -4438,18 +4462,18 @@
         <v>0</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F170">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -4458,15 +4482,15 @@
         <v>0</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F171">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -4475,98 +4499,98 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E172">
         <v>0.5</v>
       </c>
       <c r="F172">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B173">
         <v>0</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D173">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E173">
         <v>0.5</v>
       </c>
       <c r="F173">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B174">
         <v>0</v>
       </c>
       <c r="C174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D174">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E174">
         <v>0.5</v>
       </c>
       <c r="F174">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B175">
         <v>0</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D175">
         <v>0.5</v>
       </c>
       <c r="E175">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F175">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B176">
         <v>0</v>
       </c>
       <c r="C176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D176">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E176">
         <v>0.5</v>
       </c>
       <c r="F176">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4575,18 +4599,18 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4598,15 +4622,15 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4618,15 +4642,15 @@
         <v>0.5</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F179">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4638,61 +4662,61 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E181">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B182">
         <v>0</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182">
         <v>0.5</v>
       </c>
       <c r="E182">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B183">
         <v>0</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D183">
         <v>0.5</v>
@@ -4701,15 +4725,15 @@
         <v>0.5</v>
       </c>
       <c r="F183">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4721,12 +4745,12 @@
         <v>0</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -4746,13 +4770,13 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="B186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -4766,19 +4790,19 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B187">
         <v>0</v>
       </c>
       <c r="C187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -4786,10 +4810,10 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -4801,18 +4825,18 @@
         <v>0.5</v>
       </c>
       <c r="F188">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D189">
         <v>0.5</v>
@@ -4826,13 +4850,13 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="B190">
         <v>0</v>
       </c>
       <c r="C190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D190">
         <v>0.5</v>
@@ -4841,18 +4865,18 @@
         <v>0.5</v>
       </c>
       <c r="F190">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D191">
         <v>0.5</v>
@@ -4866,7 +4890,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -4875,24 +4899,24 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F192">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B193">
         <v>0</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193">
         <v>0.5</v>
@@ -4901,38 +4925,38 @@
         <v>0.5</v>
       </c>
       <c r="F193">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B194">
         <v>0</v>
       </c>
       <c r="C194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D194">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E194">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F194">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B195">
         <v>0</v>
       </c>
       <c r="C195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D195">
         <v>0</v>
@@ -4941,58 +4965,58 @@
         <v>0</v>
       </c>
       <c r="F195">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="B196">
         <v>0</v>
       </c>
       <c r="C196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D196">
         <v>0.5</v>
       </c>
       <c r="E196">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F196">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B197">
         <v>0</v>
       </c>
       <c r="C197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D197">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E197">
         <v>0</v>
       </c>
       <c r="F197">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D198">
         <v>0.5</v>
@@ -5006,13 +5030,13 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D199">
         <v>0.5</v>
@@ -5021,18 +5045,18 @@
         <v>0.5</v>
       </c>
       <c r="F199">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D200">
         <v>0.5</v>
@@ -5041,32 +5065,32 @@
         <v>0.5</v>
       </c>
       <c r="F200">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D201">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E201">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F201">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -5075,18 +5099,18 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F202">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -5095,38 +5119,38 @@
         <v>1</v>
       </c>
       <c r="D203">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E203">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F203">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F204">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -5146,7 +5170,7 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -5166,13 +5190,13 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D207">
         <v>0.5</v>
@@ -5181,12 +5205,12 @@
         <v>0.5</v>
       </c>
       <c r="F207">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -5206,7 +5230,7 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -5226,13 +5250,13 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B210">
         <v>1</v>
       </c>
       <c r="C210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D210">
         <v>0.5</v>
@@ -5241,15 +5265,15 @@
         <v>0.5</v>
       </c>
       <c r="F210">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="B211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -5261,18 +5285,18 @@
         <v>0.5</v>
       </c>
       <c r="F211">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="B212">
         <v>1</v>
       </c>
       <c r="C212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>0.5</v>
@@ -5281,38 +5305,38 @@
         <v>0.5</v>
       </c>
       <c r="F212">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="B213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E213">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F213">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="B214">
         <v>0</v>
       </c>
       <c r="C214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D214">
         <v>0.5</v>
@@ -5321,18 +5345,18 @@
         <v>0.5</v>
       </c>
       <c r="F214">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D215">
         <v>0.5</v>
@@ -5346,19 +5370,19 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B216">
         <v>0</v>
       </c>
       <c r="C216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D216">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E216">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -5366,13 +5390,13 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B217">
         <v>0</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D217">
         <v>0.5</v>
@@ -5381,12 +5405,12 @@
         <v>0.5</v>
       </c>
       <c r="F217">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B218">
         <v>0</v>
@@ -5398,21 +5422,21 @@
         <v>0.5</v>
       </c>
       <c r="E218">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F218">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B219">
         <v>1</v>
       </c>
       <c r="C219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D219">
         <v>0.5</v>
@@ -5421,12 +5445,12 @@
         <v>0.5</v>
       </c>
       <c r="F219">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -5446,7 +5470,7 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -5466,30 +5490,30 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E222">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F222">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -5501,15 +5525,15 @@
         <v>0.5</v>
       </c>
       <c r="F223">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -5521,18 +5545,18 @@
         <v>0.5</v>
       </c>
       <c r="F224">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="B225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D225">
         <v>0.5</v>
@@ -5541,18 +5565,18 @@
         <v>0.5</v>
       </c>
       <c r="F225">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B226">
         <v>1</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D226">
         <v>0.5</v>
@@ -5561,18 +5585,18 @@
         <v>0.5</v>
       </c>
       <c r="F226">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B227">
         <v>1</v>
       </c>
       <c r="C227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D227">
         <v>0.5</v>
@@ -5581,27 +5605,487 @@
         <v>0.5</v>
       </c>
       <c r="F227">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
+        <v>216</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0.5</v>
+      </c>
+      <c r="E228">
+        <v>0.5</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
+        <v>217</v>
+      </c>
+      <c r="B229">
+        <v>1</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>0.5</v>
+      </c>
+      <c r="E229">
+        <v>0.5</v>
+      </c>
+      <c r="F229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>218</v>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>0.5</v>
+      </c>
+      <c r="E230">
+        <v>0.5</v>
+      </c>
+      <c r="F230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>219</v>
+      </c>
+      <c r="B231">
+        <v>1</v>
+      </c>
+      <c r="C231">
+        <v>1</v>
+      </c>
+      <c r="D231">
+        <v>0.5</v>
+      </c>
+      <c r="E231">
+        <v>0.5</v>
+      </c>
+      <c r="F231">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>220</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232">
+        <v>1</v>
+      </c>
+      <c r="D232">
+        <v>0.5</v>
+      </c>
+      <c r="E232">
+        <v>0.5</v>
+      </c>
+      <c r="F232">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>221</v>
+      </c>
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+      <c r="D233">
+        <v>0.5</v>
+      </c>
+      <c r="E233">
+        <v>0.5</v>
+      </c>
+      <c r="F233">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>222</v>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234">
+        <v>0.5</v>
+      </c>
+      <c r="E234">
+        <v>0.5</v>
+      </c>
+      <c r="F234">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>223</v>
+      </c>
+      <c r="B235">
+        <v>0</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235">
+        <v>0.5</v>
+      </c>
+      <c r="E235">
+        <v>0.5</v>
+      </c>
+      <c r="F235">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>224</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>0.5</v>
+      </c>
+      <c r="E236">
+        <v>0.5</v>
+      </c>
+      <c r="F236">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>225</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0.5</v>
+      </c>
+      <c r="E237">
+        <v>0.5</v>
+      </c>
+      <c r="F237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>226</v>
+      </c>
+      <c r="B238">
+        <v>0</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>0.5</v>
+      </c>
+      <c r="E238">
+        <v>0.5</v>
+      </c>
+      <c r="F238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>227</v>
+      </c>
+      <c r="B239">
+        <v>0</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+      <c r="D239">
+        <v>0.5</v>
+      </c>
+      <c r="E239">
+        <v>0.5</v>
+      </c>
+      <c r="F239">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>228</v>
+      </c>
+      <c r="B240">
+        <v>1</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+      <c r="D240">
+        <v>0.5</v>
+      </c>
+      <c r="E240">
+        <v>0.5</v>
+      </c>
+      <c r="F240">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>229</v>
+      </c>
+      <c r="B241">
+        <v>1</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+      <c r="D241">
+        <v>0.5</v>
+      </c>
+      <c r="E241">
+        <v>0.5</v>
+      </c>
+      <c r="F241">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>230</v>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242">
+        <v>0.5</v>
+      </c>
+      <c r="E242">
+        <v>0.5</v>
+      </c>
+      <c r="F242">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
         <v>231</v>
       </c>
-      <c r="B228">
-        <v>1</v>
-      </c>
-      <c r="C228">
-        <v>1</v>
-      </c>
-      <c r="D228">
-        <v>0.5</v>
-      </c>
-      <c r="E228">
-        <v>0.5</v>
-      </c>
-      <c r="F228">
+      <c r="B243">
+        <v>0</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>232</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>0.5</v>
+      </c>
+      <c r="E244">
+        <v>0.5</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>233</v>
+      </c>
+      <c r="B245">
+        <v>1</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="D245">
+        <v>0.5</v>
+      </c>
+      <c r="E245">
+        <v>0.5</v>
+      </c>
+      <c r="F245">
         <v>3</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>234</v>
+      </c>
+      <c r="B246">
+        <v>0</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>0.5</v>
+      </c>
+      <c r="E246">
+        <v>0.5</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>235</v>
+      </c>
+      <c r="B247">
+        <v>1</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>0.5</v>
+      </c>
+      <c r="E247">
+        <v>0.5</v>
+      </c>
+      <c r="F247">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>236</v>
+      </c>
+      <c r="B248">
+        <v>1</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>0.5</v>
+      </c>
+      <c r="E248">
+        <v>0.5</v>
+      </c>
+      <c r="F248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" t="s">
+        <v>237</v>
+      </c>
+      <c r="B249">
+        <v>1</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+      <c r="D249">
+        <v>0.5</v>
+      </c>
+      <c r="E249">
+        <v>0.5</v>
+      </c>
+      <c r="F249">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" t="s">
+        <v>238</v>
+      </c>
+      <c r="B250">
+        <v>1</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+      <c r="D250">
+        <v>0.5</v>
+      </c>
+      <c r="E250">
+        <v>0.5</v>
+      </c>
+      <c r="F250">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" t="s">
+        <v>239</v>
+      </c>
+      <c r="B251">
+        <v>1</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>0.5</v>
+      </c>
+      <c r="E251">
+        <v>0.5</v>
+      </c>
+      <c r="F251">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/D_analysis/check_output/IC_score.xlsx
+++ b/D_analysis/check_output/IC_score.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="288">
   <si>
     <t>factor_id</t>
   </si>
@@ -568,6 +568,51 @@
     <t>O010</t>
   </si>
   <si>
+    <t>O011</t>
+  </si>
+  <si>
+    <t>O012</t>
+  </si>
+  <si>
+    <t>O013</t>
+  </si>
+  <si>
+    <t>O014</t>
+  </si>
+  <si>
+    <t>O015</t>
+  </si>
+  <si>
+    <t>O016</t>
+  </si>
+  <si>
+    <t>O017</t>
+  </si>
+  <si>
+    <t>O018</t>
+  </si>
+  <si>
+    <t>O019</t>
+  </si>
+  <si>
+    <t>O020</t>
+  </si>
+  <si>
+    <t>O021</t>
+  </si>
+  <si>
+    <t>O022</t>
+  </si>
+  <si>
+    <t>O023</t>
+  </si>
+  <si>
+    <t>O024</t>
+  </si>
+  <si>
+    <t>O025</t>
+  </si>
+  <si>
     <t>P001</t>
   </si>
   <si>
@@ -607,6 +652,99 @@
     <t>P016</t>
   </si>
   <si>
+    <t>P018</t>
+  </si>
+  <si>
+    <t>P019</t>
+  </si>
+  <si>
+    <t>P021</t>
+  </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>P033</t>
+  </si>
+  <si>
+    <t>P035</t>
+  </si>
+  <si>
+    <t>P037</t>
+  </si>
+  <si>
+    <t>P038</t>
+  </si>
+  <si>
+    <t>P039</t>
+  </si>
+  <si>
+    <t>P040</t>
+  </si>
+  <si>
+    <t>P041</t>
+  </si>
+  <si>
+    <t>P042</t>
+  </si>
+  <si>
+    <t>P043</t>
+  </si>
+  <si>
+    <t>P044</t>
+  </si>
+  <si>
+    <t>P045</t>
+  </si>
+  <si>
+    <t>P046</t>
+  </si>
+  <si>
+    <t>P047</t>
+  </si>
+  <si>
+    <t>P049</t>
+  </si>
+  <si>
+    <t>P050</t>
+  </si>
+  <si>
+    <t>P051</t>
+  </si>
+  <si>
+    <t>P052</t>
+  </si>
+  <si>
+    <t>P053</t>
+  </si>
+  <si>
+    <t>P054</t>
+  </si>
+  <si>
+    <t>P055</t>
+  </si>
+  <si>
+    <t>P056</t>
+  </si>
+  <si>
+    <t>P057</t>
+  </si>
+  <si>
+    <t>P058</t>
+  </si>
+  <si>
+    <t>P059</t>
+  </si>
+  <si>
+    <t>P060</t>
+  </si>
+  <si>
+    <t>P061</t>
+  </si>
+  <si>
     <t>V001</t>
   </si>
   <si>
@@ -734,6 +872,12 @@
   </si>
   <si>
     <t>W006_binary</t>
+  </si>
+  <si>
+    <t>W007_binary</t>
+  </si>
+  <si>
+    <t>W008_binary</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F251"/>
+  <dimension ref="A1:F308"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2373,10 +2517,10 @@
         <v>70</v>
       </c>
       <c r="B66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
         <v>0.5</v>
@@ -2413,7 +2557,7 @@
         <v>70</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -2425,15 +2569,15 @@
         <v>0.5</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -2442,10 +2586,10 @@
         <v>0.5</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F69">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2476,16 +2620,16 @@
         <v>0</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2496,21 +2640,21 @@
         <v>0</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -2519,18 +2663,18 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2539,141 +2683,141 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B75">
         <v>0</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>0.5</v>
       </c>
       <c r="E75">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B77">
         <v>0</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E77">
         <v>0.5</v>
       </c>
       <c r="F77">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2685,24 +2829,24 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -2710,13 +2854,13 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B83">
         <v>0</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -2725,15 +2869,15 @@
         <v>0</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2745,38 +2889,38 @@
         <v>0</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -2785,58 +2929,58 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B87">
         <v>0</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B88">
         <v>0</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -2845,38 +2989,38 @@
         <v>0</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E90">
         <v>0.5</v>
       </c>
       <c r="F90">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -2885,58 +3029,58 @@
         <v>0</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E92">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>0.5</v>
       </c>
       <c r="F93">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B94">
         <v>0</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -2945,52 +3089,52 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F96">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -3010,13 +3154,13 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -3030,10 +3174,10 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -3042,15 +3186,15 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3059,18 +3203,18 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3090,53 +3234,53 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B102">
         <v>0</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>0.5</v>
       </c>
       <c r="F102">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B103">
         <v>0</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0.5</v>
       </c>
       <c r="E103">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F103">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B104">
         <v>0</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -3145,12 +3289,12 @@
         <v>0</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3170,7 +3314,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3190,33 +3334,33 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B107">
         <v>0</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F107">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108">
         <v>0.5</v>
@@ -3230,7 +3374,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3250,7 +3394,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3259,24 +3403,24 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E110">
         <v>0.5</v>
       </c>
       <c r="F110">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0.5</v>
@@ -3290,27 +3434,27 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3319,38 +3463,38 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0.5</v>
       </c>
       <c r="F113">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B114">
         <v>0</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3359,18 +3503,18 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F115">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3379,44 +3523,44 @@
         <v>1</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F116">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B117">
         <v>0</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
         <v>0.5</v>
@@ -3425,58 +3569,58 @@
         <v>0.5</v>
       </c>
       <c r="F118">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F119">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121">
         <v>0.5</v>
@@ -3485,38 +3629,38 @@
         <v>0.5</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -3525,24 +3669,24 @@
         <v>0</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -3550,39 +3694,39 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B125">
         <v>0</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E125">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -3590,13 +3734,13 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -3610,39 +3754,39 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128">
         <v>0.5</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F128">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -3650,7 +3794,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -3670,27 +3814,27 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E131">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F131">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -3699,21 +3843,21 @@
         <v>1</v>
       </c>
       <c r="D132">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E132">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F132">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -3725,12 +3869,12 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -3739,21 +3883,21 @@
         <v>1</v>
       </c>
       <c r="D134">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E134">
         <v>0.5</v>
       </c>
       <c r="F134">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -3765,32 +3909,32 @@
         <v>0.5</v>
       </c>
       <c r="F135">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F136">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -3810,7 +3954,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -3830,7 +3974,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -3850,30 +3994,30 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E140">
         <v>0.5</v>
       </c>
       <c r="F140">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -3885,158 +4029,158 @@
         <v>0.5</v>
       </c>
       <c r="F141">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E142">
         <v>0.5</v>
       </c>
       <c r="F142">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E143">
         <v>0.5</v>
       </c>
       <c r="F143">
-        <v>0.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F144">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>0.5</v>
       </c>
       <c r="F145">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B146">
         <v>0</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E146">
         <v>0.5</v>
       </c>
       <c r="F146">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B147">
         <v>0</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B148">
         <v>0</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F148">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -4045,32 +4189,32 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -4090,7 +4234,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -4099,21 +4243,21 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E152">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F152">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -4125,24 +4269,24 @@
         <v>0</v>
       </c>
       <c r="F153">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E154">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>2</v>
@@ -4150,7 +4294,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -4159,44 +4303,44 @@
         <v>1</v>
       </c>
       <c r="D155">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F155">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B156">
         <v>0</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E156">
         <v>0.5</v>
       </c>
       <c r="F156">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B157">
         <v>0</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157">
         <v>0.5</v>
@@ -4205,15 +4349,15 @@
         <v>0.5</v>
       </c>
       <c r="F157">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -4225,98 +4369,98 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B159">
         <v>0</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E159">
         <v>0.5</v>
       </c>
       <c r="F159">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B160">
         <v>0</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E160">
         <v>0.5</v>
       </c>
       <c r="F160">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B161">
         <v>0</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B162">
         <v>0</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B163">
         <v>0</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163">
         <v>0.5</v>
@@ -4325,92 +4469,92 @@
         <v>0.5</v>
       </c>
       <c r="F163">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B164">
         <v>0</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D164">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B165">
         <v>0</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E165">
         <v>0.5</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B166">
         <v>0</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E166">
         <v>0.5</v>
       </c>
       <c r="F166">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B167">
         <v>0</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E167">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F167">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -4419,38 +4563,38 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E168">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F168">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B169">
         <v>0</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169">
         <v>0.5</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F169">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -4459,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E170">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>0.5</v>
@@ -4470,67 +4614,67 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B171">
         <v>0</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E171">
         <v>0.5</v>
       </c>
       <c r="F171">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B172">
         <v>0</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E172">
         <v>0.5</v>
       </c>
       <c r="F172">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B173">
         <v>0</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E173">
         <v>0.5</v>
       </c>
       <c r="F173">
-        <v>0.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -4539,24 +4683,24 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E174">
         <v>0.5</v>
       </c>
       <c r="F174">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B175">
         <v>0</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D175">
         <v>0.5</v>
@@ -4565,12 +4709,12 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -4590,7 +4734,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -4599,10 +4743,10 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F177">
         <v>0.5</v>
@@ -4610,7 +4754,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -4630,7 +4774,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -4639,18 +4783,18 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E179">
         <v>0.5</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -4670,70 +4814,70 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C181">
         <v>0</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E181">
         <v>0</v>
       </c>
       <c r="F181">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B182">
         <v>0</v>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F182">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B183">
         <v>0</v>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D183">
         <v>0.5</v>
       </c>
       <c r="E183">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F183">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -4742,27 +4886,27 @@
         <v>0</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F184">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C185">
         <v>0</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -4770,10 +4914,10 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -4782,27 +4926,27 @@
         <v>0</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F186">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C187">
         <v>0</v>
       </c>
       <c r="D187">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -4810,7 +4954,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -4822,15 +4966,15 @@
         <v>0.5</v>
       </c>
       <c r="E188">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F188">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -4850,19 +4994,19 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C190">
         <v>0</v>
       </c>
       <c r="D190">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -4870,53 +5014,53 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D191">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E192">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F192">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B193">
         <v>0</v>
       </c>
       <c r="C193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D193">
         <v>0.5</v>
@@ -4925,58 +5069,58 @@
         <v>0.5</v>
       </c>
       <c r="F193">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B194">
         <v>0</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B195">
         <v>0</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B196">
         <v>0</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196">
         <v>0.5</v>
@@ -4985,12 +5129,12 @@
         <v>0</v>
       </c>
       <c r="F196">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B197">
         <v>0</v>
@@ -4999,44 +5143,44 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B198">
         <v>0</v>
       </c>
       <c r="C198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D198">
         <v>0.5</v>
       </c>
       <c r="E198">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F198">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B199">
         <v>0</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D199">
         <v>0.5</v>
@@ -5045,12 +5189,12 @@
         <v>0.5</v>
       </c>
       <c r="F199">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -5059,24 +5203,24 @@
         <v>0</v>
       </c>
       <c r="D200">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E200">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F200">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B201">
         <v>0</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D201">
         <v>0</v>
@@ -5085,38 +5229,38 @@
         <v>0</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F202">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B203">
         <v>0</v>
       </c>
       <c r="C203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -5125,18 +5269,18 @@
         <v>0</v>
       </c>
       <c r="F203">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B204">
         <v>0</v>
       </c>
       <c r="C204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -5145,107 +5289,107 @@
         <v>0</v>
       </c>
       <c r="F204">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E205">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F205">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D206">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E206">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F206">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D207">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E207">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F207">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208">
         <v>0</v>
       </c>
       <c r="D208">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E208">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F208">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209">
         <v>0</v>
       </c>
       <c r="D209">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E209">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F209">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -5253,19 +5397,19 @@
         <v>198</v>
       </c>
       <c r="B210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C210">
         <v>0</v>
       </c>
       <c r="D210">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E210">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F210">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -5290,13 +5434,13 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D212">
         <v>0.5</v>
@@ -5310,7 +5454,7 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B213">
         <v>0</v>
@@ -5319,24 +5463,24 @@
         <v>1</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E213">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F213">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B214">
         <v>0</v>
       </c>
       <c r="C214">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D214">
         <v>0.5</v>
@@ -5345,12 +5489,12 @@
         <v>0.5</v>
       </c>
       <c r="F214">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B215">
         <v>0</v>
@@ -5370,13 +5514,13 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B216">
         <v>0</v>
       </c>
       <c r="C216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D216">
         <v>0</v>
@@ -5385,38 +5529,38 @@
         <v>0</v>
       </c>
       <c r="F216">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B217">
         <v>0</v>
       </c>
       <c r="C217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D217">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E217">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F217">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B218">
         <v>0</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218">
         <v>0.5</v>
@@ -5425,35 +5569,35 @@
         <v>0</v>
       </c>
       <c r="F218">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C219">
         <v>0</v>
       </c>
       <c r="D219">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E219">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F219">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C220">
         <v>1</v>
@@ -5465,18 +5609,18 @@
         <v>0.5</v>
       </c>
       <c r="F220">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D221">
         <v>0.5</v>
@@ -5485,18 +5629,18 @@
         <v>0.5</v>
       </c>
       <c r="F221">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D222">
         <v>0.5</v>
@@ -5505,95 +5649,95 @@
         <v>0.5</v>
       </c>
       <c r="F222">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C223">
         <v>0</v>
       </c>
       <c r="D223">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E223">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F223">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D224">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E224">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F224">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E225">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F225">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E226">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F226">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -5605,18 +5749,18 @@
         <v>0.5</v>
       </c>
       <c r="F227">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B228">
         <v>0</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D228">
         <v>0.5</v>
@@ -5625,18 +5769,18 @@
         <v>0.5</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B229">
         <v>1</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D229">
         <v>0.5</v>
@@ -5645,18 +5789,18 @@
         <v>0.5</v>
       </c>
       <c r="F229">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D230">
         <v>0.5</v>
@@ -5670,30 +5814,30 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E231">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F231">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -5705,12 +5849,12 @@
         <v>0.5</v>
       </c>
       <c r="F232">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -5730,27 +5874,27 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E234">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F234">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B235">
         <v>0</v>
@@ -5770,39 +5914,39 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C236">
         <v>0</v>
       </c>
       <c r="D236">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E236">
         <v>0.5</v>
       </c>
       <c r="F236">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B237">
         <v>0</v>
       </c>
       <c r="C237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D237">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E237">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F237">
         <v>1</v>
@@ -5810,7 +5954,7 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B238">
         <v>0</v>
@@ -5819,18 +5963,18 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E238">
         <v>0.5</v>
       </c>
       <c r="F238">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B239">
         <v>0</v>
@@ -5850,13 +5994,13 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D240">
         <v>0.5</v>
@@ -5865,35 +6009,35 @@
         <v>0.5</v>
       </c>
       <c r="F240">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B241">
         <v>1</v>
       </c>
       <c r="C241">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D241">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E241">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F241">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -5905,32 +6049,32 @@
         <v>0.5</v>
       </c>
       <c r="F242">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B243">
         <v>0</v>
       </c>
       <c r="C243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D243">
         <v>0</v>
       </c>
       <c r="E243">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F243">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B244">
         <v>0</v>
@@ -5950,33 +6094,33 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E245">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F245">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D246">
         <v>0.5</v>
@@ -5985,12 +6129,12 @@
         <v>0.5</v>
       </c>
       <c r="F246">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -5999,92 +6143,1232 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E247">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F247">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E248">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F248">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D249">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>0.5</v>
       </c>
       <c r="F249">
-        <v>3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B250">
         <v>1</v>
       </c>
       <c r="C250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D250">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E250">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F250">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
+        <v>236</v>
+      </c>
+      <c r="B251">
+        <v>0</v>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" t="s">
+        <v>237</v>
+      </c>
+      <c r="B252">
+        <v>0</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0.5</v>
+      </c>
+      <c r="F252">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" t="s">
+        <v>238</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>0.5</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" t="s">
         <v>239</v>
       </c>
-      <c r="B251">
-        <v>1</v>
-      </c>
-      <c r="C251">
-        <v>0</v>
-      </c>
-      <c r="D251">
-        <v>0.5</v>
-      </c>
-      <c r="E251">
-        <v>0.5</v>
-      </c>
-      <c r="F251">
+      <c r="B254">
+        <v>0</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" t="s">
+        <v>240</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" t="s">
+        <v>241</v>
+      </c>
+      <c r="B256">
+        <v>0</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" t="s">
+        <v>242</v>
+      </c>
+      <c r="B257">
+        <v>0</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" t="s">
+        <v>243</v>
+      </c>
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258">
+        <v>1</v>
+      </c>
+      <c r="D258">
+        <v>0.5</v>
+      </c>
+      <c r="E258">
+        <v>0.5</v>
+      </c>
+      <c r="F258">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" t="s">
+        <v>243</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259">
+        <v>1</v>
+      </c>
+      <c r="D259">
+        <v>0.5</v>
+      </c>
+      <c r="E259">
+        <v>0.5</v>
+      </c>
+      <c r="F259">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" t="s">
+        <v>243</v>
+      </c>
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260">
+        <v>0.5</v>
+      </c>
+      <c r="E260">
+        <v>0.5</v>
+      </c>
+      <c r="F260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" t="s">
+        <v>243</v>
+      </c>
+      <c r="B261">
+        <v>1</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+      <c r="D261">
+        <v>0.5</v>
+      </c>
+      <c r="E261">
+        <v>0.5</v>
+      </c>
+      <c r="F261">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" t="s">
+        <v>244</v>
+      </c>
+      <c r="B262">
+        <v>1</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>0.5</v>
+      </c>
+      <c r="E262">
+        <v>0.5</v>
+      </c>
+      <c r="F262">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" t="s">
+        <v>244</v>
+      </c>
+      <c r="B263">
+        <v>1</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>0.5</v>
+      </c>
+      <c r="E263">
+        <v>0.5</v>
+      </c>
+      <c r="F263">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" t="s">
+        <v>244</v>
+      </c>
+      <c r="B264">
+        <v>1</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>0.5</v>
+      </c>
+      <c r="E264">
+        <v>0.5</v>
+      </c>
+      <c r="F264">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" t="s">
+        <v>244</v>
+      </c>
+      <c r="B265">
+        <v>1</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>0.5</v>
+      </c>
+      <c r="E265">
+        <v>0.5</v>
+      </c>
+      <c r="F265">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" t="s">
+        <v>245</v>
+      </c>
+      <c r="B266">
+        <v>0</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+      <c r="D266">
+        <v>0.5</v>
+      </c>
+      <c r="E266">
+        <v>0.5</v>
+      </c>
+      <c r="F266">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" t="s">
+        <v>246</v>
+      </c>
+      <c r="B267">
+        <v>1</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>0.5</v>
+      </c>
+      <c r="E267">
+        <v>0.5</v>
+      </c>
+      <c r="F267">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" t="s">
+        <v>247</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>1</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" t="s">
+        <v>248</v>
+      </c>
+      <c r="B269">
+        <v>0</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>0.5</v>
+      </c>
+      <c r="E269">
+        <v>0.5</v>
+      </c>
+      <c r="F269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" t="s">
+        <v>249</v>
+      </c>
+      <c r="B270">
+        <v>0</v>
+      </c>
+      <c r="C270">
+        <v>1</v>
+      </c>
+      <c r="D270">
+        <v>0.5</v>
+      </c>
+      <c r="E270">
+        <v>0.5</v>
+      </c>
+      <c r="F270">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" t="s">
+        <v>250</v>
+      </c>
+      <c r="B271">
+        <v>0</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" t="s">
+        <v>251</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272">
+        <v>0.5</v>
+      </c>
+      <c r="E272">
+        <v>0.5</v>
+      </c>
+      <c r="F272">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
+        <v>252</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>1</v>
+      </c>
+      <c r="D273">
+        <v>0.5</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
+        <v>253</v>
+      </c>
+      <c r="B274">
+        <v>1</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>0.5</v>
+      </c>
+      <c r="E274">
+        <v>0.5</v>
+      </c>
+      <c r="F274">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
+        <v>254</v>
+      </c>
+      <c r="B275">
+        <v>1</v>
+      </c>
+      <c r="C275">
+        <v>1</v>
+      </c>
+      <c r="D275">
+        <v>0.5</v>
+      </c>
+      <c r="E275">
+        <v>0.5</v>
+      </c>
+      <c r="F275">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
+        <v>255</v>
+      </c>
+      <c r="B276">
+        <v>1</v>
+      </c>
+      <c r="C276">
+        <v>1</v>
+      </c>
+      <c r="D276">
+        <v>0.5</v>
+      </c>
+      <c r="E276">
+        <v>0.5</v>
+      </c>
+      <c r="F276">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
+        <v>256</v>
+      </c>
+      <c r="B277">
+        <v>1</v>
+      </c>
+      <c r="C277">
+        <v>1</v>
+      </c>
+      <c r="D277">
+        <v>0.5</v>
+      </c>
+      <c r="E277">
+        <v>0.5</v>
+      </c>
+      <c r="F277">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
+        <v>257</v>
+      </c>
+      <c r="B278">
+        <v>1</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>0.5</v>
+      </c>
+      <c r="E278">
+        <v>0.5</v>
+      </c>
+      <c r="F278">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
+        <v>258</v>
+      </c>
+      <c r="B279">
+        <v>0</v>
+      </c>
+      <c r="C279">
+        <v>1</v>
+      </c>
+      <c r="D279">
+        <v>0.5</v>
+      </c>
+      <c r="E279">
+        <v>0.5</v>
+      </c>
+      <c r="F279">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>259</v>
+      </c>
+      <c r="B280">
+        <v>1</v>
+      </c>
+      <c r="C280">
+        <v>1</v>
+      </c>
+      <c r="D280">
+        <v>0.5</v>
+      </c>
+      <c r="E280">
+        <v>0.5</v>
+      </c>
+      <c r="F280">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>260</v>
+      </c>
+      <c r="B281">
+        <v>1</v>
+      </c>
+      <c r="C281">
+        <v>1</v>
+      </c>
+      <c r="D281">
+        <v>0.5</v>
+      </c>
+      <c r="E281">
+        <v>0.5</v>
+      </c>
+      <c r="F281">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>261</v>
+      </c>
+      <c r="B282">
+        <v>1</v>
+      </c>
+      <c r="C282">
+        <v>1</v>
+      </c>
+      <c r="D282">
+        <v>0.5</v>
+      </c>
+      <c r="E282">
+        <v>0.5</v>
+      </c>
+      <c r="F282">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>262</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>0.5</v>
+      </c>
+      <c r="E283">
+        <v>0.5</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>263</v>
+      </c>
+      <c r="B284">
+        <v>1</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>0.5</v>
+      </c>
+      <c r="E284">
+        <v>0.5</v>
+      </c>
+      <c r="F284">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>264</v>
+      </c>
+      <c r="B285">
+        <v>1</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>0.5</v>
+      </c>
+      <c r="E285">
+        <v>0.5</v>
+      </c>
+      <c r="F285">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>265</v>
+      </c>
+      <c r="B286">
+        <v>1</v>
+      </c>
+      <c r="C286">
+        <v>1</v>
+      </c>
+      <c r="D286">
+        <v>0.5</v>
+      </c>
+      <c r="E286">
+        <v>0.5</v>
+      </c>
+      <c r="F286">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>266</v>
+      </c>
+      <c r="B287">
+        <v>1</v>
+      </c>
+      <c r="C287">
+        <v>1</v>
+      </c>
+      <c r="D287">
+        <v>0.5</v>
+      </c>
+      <c r="E287">
+        <v>0.5</v>
+      </c>
+      <c r="F287">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>267</v>
+      </c>
+      <c r="B288">
+        <v>1</v>
+      </c>
+      <c r="C288">
+        <v>1</v>
+      </c>
+      <c r="D288">
+        <v>0.5</v>
+      </c>
+      <c r="E288">
+        <v>0.5</v>
+      </c>
+      <c r="F288">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>268</v>
+      </c>
+      <c r="B289">
+        <v>1</v>
+      </c>
+      <c r="C289">
+        <v>1</v>
+      </c>
+      <c r="D289">
+        <v>0.5</v>
+      </c>
+      <c r="E289">
+        <v>0.5</v>
+      </c>
+      <c r="F289">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>269</v>
+      </c>
+      <c r="B290">
+        <v>0</v>
+      </c>
+      <c r="C290">
+        <v>1</v>
+      </c>
+      <c r="D290">
+        <v>0.5</v>
+      </c>
+      <c r="E290">
+        <v>0.5</v>
+      </c>
+      <c r="F290">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>270</v>
+      </c>
+      <c r="B291">
+        <v>1</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0.5</v>
+      </c>
+      <c r="E291">
+        <v>0.5</v>
+      </c>
+      <c r="F291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>271</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>0.5</v>
+      </c>
+      <c r="E292">
+        <v>0.5</v>
+      </c>
+      <c r="F292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" t="s">
+        <v>272</v>
+      </c>
+      <c r="B293">
+        <v>0</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>0.5</v>
+      </c>
+      <c r="E293">
+        <v>0.5</v>
+      </c>
+      <c r="F293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" t="s">
+        <v>273</v>
+      </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
+      <c r="C294">
+        <v>1</v>
+      </c>
+      <c r="D294">
+        <v>0.5</v>
+      </c>
+      <c r="E294">
+        <v>0.5</v>
+      </c>
+      <c r="F294">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" t="s">
+        <v>274</v>
+      </c>
+      <c r="B295">
+        <v>1</v>
+      </c>
+      <c r="C295">
+        <v>1</v>
+      </c>
+      <c r="D295">
+        <v>0.5</v>
+      </c>
+      <c r="E295">
+        <v>0.5</v>
+      </c>
+      <c r="F295">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" t="s">
+        <v>275</v>
+      </c>
+      <c r="B296">
+        <v>1</v>
+      </c>
+      <c r="C296">
+        <v>1</v>
+      </c>
+      <c r="D296">
+        <v>0.5</v>
+      </c>
+      <c r="E296">
+        <v>0.5</v>
+      </c>
+      <c r="F296">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" t="s">
+        <v>276</v>
+      </c>
+      <c r="B297">
+        <v>1</v>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+      <c r="D297">
+        <v>0.5</v>
+      </c>
+      <c r="E297">
+        <v>0.5</v>
+      </c>
+      <c r="F297">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" t="s">
+        <v>277</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+      <c r="C298">
+        <v>1</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" t="s">
+        <v>278</v>
+      </c>
+      <c r="B299">
+        <v>0</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>0.5</v>
+      </c>
+      <c r="E299">
+        <v>0.5</v>
+      </c>
+      <c r="F299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" t="s">
+        <v>279</v>
+      </c>
+      <c r="B300">
+        <v>1</v>
+      </c>
+      <c r="C300">
+        <v>1</v>
+      </c>
+      <c r="D300">
+        <v>0.5</v>
+      </c>
+      <c r="E300">
+        <v>0.5</v>
+      </c>
+      <c r="F300">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" t="s">
+        <v>280</v>
+      </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>0.5</v>
+      </c>
+      <c r="E301">
+        <v>0.5</v>
+      </c>
+      <c r="F301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" t="s">
+        <v>281</v>
+      </c>
+      <c r="B302">
+        <v>1</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>0.5</v>
+      </c>
+      <c r="E302">
+        <v>0.5</v>
+      </c>
+      <c r="F302">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" t="s">
+        <v>282</v>
+      </c>
+      <c r="B303">
+        <v>1</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>0.5</v>
+      </c>
+      <c r="E303">
+        <v>0.5</v>
+      </c>
+      <c r="F303">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" t="s">
+        <v>283</v>
+      </c>
+      <c r="B304">
+        <v>1</v>
+      </c>
+      <c r="C304">
+        <v>1</v>
+      </c>
+      <c r="D304">
+        <v>0.5</v>
+      </c>
+      <c r="E304">
+        <v>0.5</v>
+      </c>
+      <c r="F304">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" t="s">
+        <v>284</v>
+      </c>
+      <c r="B305">
+        <v>1</v>
+      </c>
+      <c r="C305">
+        <v>1</v>
+      </c>
+      <c r="D305">
+        <v>0.5</v>
+      </c>
+      <c r="E305">
+        <v>0.5</v>
+      </c>
+      <c r="F305">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" t="s">
+        <v>285</v>
+      </c>
+      <c r="B306">
+        <v>1</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>0.5</v>
+      </c>
+      <c r="E306">
+        <v>0.5</v>
+      </c>
+      <c r="F306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" t="s">
+        <v>286</v>
+      </c>
+      <c r="B307">
+        <v>1</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>0.5</v>
+      </c>
+      <c r="E307">
+        <v>0.5</v>
+      </c>
+      <c r="F307">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" t="s">
+        <v>287</v>
+      </c>
+      <c r="B308">
+        <v>1</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0.5</v>
+      </c>
+      <c r="E308">
+        <v>0.5</v>
+      </c>
+      <c r="F308">
         <v>2</v>
       </c>
     </row>
